--- a/inst/testdata/examples_of_output/testoutput_ejamit_fips_counties.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejamit_fips_counties.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Locations analyzed</t>
   </si>
   <si>
-    <t xml:space="preserve">Census Units defined by FIPS code</t>
+    <t xml:space="preserve">Selected Locations</t>
   </si>
   <si>
     <t xml:space="preserve">Distance in miles</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">Distance type</t>
   </si>
   <si>
-    <t xml:space="preserve">Miles radius of circular buffer (or distance used if buffering around polygons)</t>
+    <t xml:space="preserve">Residents within any of the 3 specified counties. Area in Square Miles: 1948.54</t>
   </si>
   <si>
     <t xml:space="preserve">Population at x% of sites</t>
   </si>
   <si>
-    <t xml:space="preserve">0% of places account for 50% of the total population (approx.)</t>
+    <t xml:space="preserve">The most-populated 33% of the 3 places can account for at least 50% of the total population of all sites as a whole.</t>
   </si>
   <si>
     <t xml:space="preserve">Population at N sites</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10001&amp;buffer=0&amp;sitenumber=-1&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10001&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.1200058983347,-75.5510430230294", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
@@ -1517,7 +1517,7 @@
     <t xml:space="preserve">Delaware</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10003&amp;buffer=0&amp;sitenumber=-1&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10003&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.6941830363225,-75.6221648888872", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">10003</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10005&amp;buffer=0&amp;sitenumber=-1&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10005&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=38.6589904545443,-75.2827937131076", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
@@ -5906,7 +5906,7 @@
         <v>0.956101615858054</v>
       </c>
       <c r="P2" s="28" t="n">
-        <v>0.467815382398318</v>
+        <v>0.467815382398319</v>
       </c>
       <c r="Q2" s="28" t="n">
         <v>1.05673743211302</v>
@@ -5954,7 +5954,7 @@
         <v>0.982155716776445</v>
       </c>
       <c r="AF2" s="28" t="n">
-        <v>0.647141133584071</v>
+        <v>0.64714113358407</v>
       </c>
       <c r="AG2" s="28" t="n">
         <v>0.574530628558404</v>
@@ -6227,7 +6227,7 @@
         <v>0.208928564078605</v>
       </c>
       <c r="DS2" s="30" t="n">
-        <v>6.07533607456141</v>
+        <v>6.0753360745614</v>
       </c>
       <c r="DT2" s="24" t="n">
         <v>11.3695740131579</v>
@@ -6263,7 +6263,7 @@
         <v>60.7459284773026</v>
       </c>
       <c r="EE2" s="23" t="n">
-        <v>5.07775335284309</v>
+        <v>5.0777533528431</v>
       </c>
       <c r="EF2" s="25" t="n">
         <v>0.109777051144313</v>
@@ -7332,7 +7332,7 @@
         <v>0.963846404476376</v>
       </c>
       <c r="AG3" s="28" t="n">
-        <v>0.975229372534115</v>
+        <v>0.975229372534116</v>
       </c>
       <c r="AH3" s="28" t="n">
         <v>1.37490188099129</v>
@@ -7371,7 +7371,7 @@
         <v>1.06421005348864</v>
       </c>
       <c r="AT3" s="28" t="n">
-        <v>0.920152012532016</v>
+        <v>0.920152012532015</v>
       </c>
       <c r="AU3" s="28" t="n">
         <v>0.918982081928526</v>
@@ -8495,7 +8495,7 @@
         <v>47.7544453150353</v>
       </c>
       <c r="PL3" s="25" t="n">
-        <v>96.8128969723428</v>
+        <v>96.8128969723427</v>
       </c>
       <c r="PM3" s="25" t="n">
         <v>74.4067227121011</v>
@@ -8671,7 +8671,7 @@
         <v>1.63944073894476</v>
       </c>
       <c r="U4" s="28" t="n">
-        <v>0.646553246094324</v>
+        <v>0.646553246094323</v>
       </c>
       <c r="V4" s="28" t="n">
         <v>0.535345838620863</v>
@@ -8728,7 +8728,7 @@
         <v>0.105327088823987</v>
       </c>
       <c r="AN4" s="28" t="n">
-        <v>0.269675510676167</v>
+        <v>0.269675510676166</v>
       </c>
       <c r="AO4" s="28" t="n">
         <v>0.000243073850861005</v>
@@ -8830,7 +8830,7 @@
         <v>0.0164210335130008</v>
       </c>
       <c r="BV4" s="28" t="n">
-        <v>0.442571873800101</v>
+        <v>0.442571873800102</v>
       </c>
       <c r="BW4" s="28" t="n">
         <v>1.04441724394198</v>
@@ -8848,7 +8848,7 @@
         <v>0.269582622253123</v>
       </c>
       <c r="CB4" s="30" t="n">
-        <v>0.0229225500210299</v>
+        <v>0.0229225500210298</v>
       </c>
       <c r="CC4" s="30" t="n">
         <v>0.0482641829749086</v>
@@ -9037,7 +9037,7 @@
         <v>0.372395162805404</v>
       </c>
       <c r="EM4" s="23" t="n">
-        <v>0.980939788114327</v>
+        <v>0.980939788114326</v>
       </c>
       <c r="EN4" s="22" t="n">
         <v>170.590546829038</v>
@@ -9942,13 +9942,13 @@
         <v>63.4434107788934</v>
       </c>
       <c r="QJ4" s="25" t="n">
-        <v>69.9678414811887</v>
+        <v>69.9678414811886</v>
       </c>
       <c r="QK4" s="25" t="n">
         <v>10.0091788073496</v>
       </c>
       <c r="QL4" s="25" t="n">
-        <v>43.2434571110145</v>
+        <v>43.2434571110144</v>
       </c>
       <c r="QM4" s="25" t="n">
         <v>29.771955636353</v>
@@ -11741,7 +11741,7 @@
         <v>0.303757776624197</v>
       </c>
       <c r="Z2" s="28" t="n">
-        <v>0.168440088818039</v>
+        <v>0.16844008881804</v>
       </c>
       <c r="AA2" s="28" t="n">
         <v>1.06577427364379</v>
@@ -12268,7 +12268,7 @@
         <v>54.9569298585497</v>
       </c>
       <c r="GW2" s="29" t="n">
-        <v>74.5742219225369</v>
+        <v>74.574221922537</v>
       </c>
       <c r="GX2" s="29" t="n">
         <v>62.6405078323529</v>
@@ -12810,7 +12810,7 @@
         <v>55.7526616916675</v>
       </c>
       <c r="NY2" s="29" t="n">
-        <v>55.0736678961591</v>
+        <v>55.073667896159</v>
       </c>
       <c r="NZ2" s="29" t="n">
         <v>54.5501607733222</v>
@@ -12898,7 +12898,7 @@
         <v>58.3419603425423</v>
       </c>
       <c r="PC2" s="25" t="n">
-        <v>67.4414499125401</v>
+        <v>67.44144991254</v>
       </c>
       <c r="PD2" s="25" t="n">
         <v>57.3648133098042</v>
@@ -12973,7 +12973,7 @@
         <v>56.9595237798071</v>
       </c>
       <c r="QB2" s="25" t="n">
-        <v>67.8671601294424</v>
+        <v>67.8671601294425</v>
       </c>
       <c r="QC2" s="25" t="n">
         <v>78.2320507616794</v>
@@ -13027,7 +13027,7 @@
         <v>68.3701242002911</v>
       </c>
       <c r="QT2" s="25" t="n">
-        <v>65.2750443914759</v>
+        <v>65.275044391476</v>
       </c>
       <c r="QU2" s="25" t="n">
         <v>67.26533549095</v>

--- a/inst/testdata/examples_of_output/testoutput_ejamit_fips_counties.xlsx
+++ b/inst/testdata/examples_of_output/testoutput_ejamit_fips_counties.xlsx
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">area_sqmi</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejanalysis.com", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejanalysis.com" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">https://pedp-ejscreen.azurewebsites.net/index.html</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10001&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.1200058983347,-75.5510430230294", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10001&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.1200058983347,-75.5510430230294" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">10001</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">Delaware</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10003&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.6941830363225,-75.6221648888872", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10003&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=39.6941830363225,-75.6221648888872" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">10003</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10005&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE", target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=38.6589904545443,-75.2827937131076", target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
+    <t xml:space="preserve">&lt;a href="https://ejamapi-84652557241.us-central1.run.app/report?fips=10005&amp;buffer=0&amp;sitetype=fips&amp;validate_regids=FALSE" target="_blank"&gt;EJAM Site Report&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;a href="https://pedp-ejscreen.azurewebsites.net/index.html?wherestr=38.6589904545443,-75.2827937131076" target="_blank"&gt;EJSCREEN&lt;/a&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">10005</t>
